--- a/자리표.xlsx
+++ b/자리표.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,102 +461,156 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>이명자</t>
+          <t>김나연</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이보람</t>
+          <t>김승연</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>장하윤</t>
+          <t>임다인</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>성정호</t>
+          <t>이예빈</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>박옥순</t>
+          <t>이지예</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>윤은정</t>
+          <t>강건우</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>윤서윤</t>
+          <t>김예담</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>박정순</t>
+          <t>장서윤</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>김현우</t>
+          <t>최세희</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>이영일</t>
+          <t>장윤서</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>김은경</t>
+          <t>이나연</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이은경</t>
+          <t>조하진</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>김미영</t>
+          <t>장윤성</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>윤수진</t>
+          <t>김지호</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>임승민</t>
+          <t>백지우</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>김나경</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>신우진</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>이성현</t>
+          <t>반주은</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>박상훈</t>
+          <t>김소아</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>이상호</t>
-        </is>
-      </c>
+          <t>박세은</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>정예원</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>정미지</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>이동진</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>고동연</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>한예린</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>이완희</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>오서진</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>정서윤</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -569,140 +623,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>이상호</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>박상훈</t>
-        </is>
-      </c>
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr"/>
       <c r="C1" t="inlineStr">
         <is>
-          <t>이성현</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
+          <t>정서윤</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>오서진</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>이완희</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>임승민</t>
+          <t>한예린</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>윤수진</t>
+          <t>고동연</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>김미영</t>
+          <t>이동진</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이은경</t>
+          <t>정미지</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>김은경</t>
+          <t>정예원</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>이영일</t>
+          <t>박세은</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>김현우</t>
+          <t>김소아</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>박정순</t>
+          <t>반주은</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>윤서윤</t>
+          <t>신우진</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>윤은정</t>
+          <t>김나경</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>박옥순</t>
+          <t>백지우</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>성정호</t>
+          <t>김지호</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>장하윤</t>
+          <t>장윤성</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이보람</t>
+          <t>조하진</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>이명자</t>
+          <t>이나연</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>장윤서</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>최세희</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>장서윤</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>김예담</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>강건우</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>칠판</t>
+          <t>이지예</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>칠판</t>
+          <t>이예빈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>칠판</t>
+          <t>임다인</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>칠판</t>
+          <t>김승연</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>칠판</t>
+          <t>김나연</t>
         </is>
       </c>
     </row>
@@ -713,6 +787,40 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/자리표.xlsx
+++ b/자리표.xlsx
@@ -461,152 +461,152 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>김나연</t>
+          <t>정예원</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>김승연</t>
+          <t>장윤성</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>임다인</t>
+          <t>백지우</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이예빈</t>
+          <t>반주은</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>이지예</t>
+          <t>한예린</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>강건우</t>
+          <t>장서윤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>김나연</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>이동진</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>김예담</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>장서윤</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>최세희</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>장윤서</t>
+          <t>김승연</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>임다인</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>김나경</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>조하진</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>장윤서</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>이나연</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>조하진</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>장윤성</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>김지호</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>백지우</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>김나경</t>
+          <t>신우진</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>신우진</t>
+          <t>이지예</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>반주은</t>
+          <t>김지호</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>김소아</t>
+          <t>박세은</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>박세은</t>
+          <t>강건우</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>정예원</t>
+          <t>정미지</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>정미지</t>
+          <t>고동연</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>이동진</t>
+          <t>김소아</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>고동연</t>
+          <t>최세희</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>한예린</t>
+          <t>오서진</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>정서윤</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>이예빈</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>이완희</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>오서진</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>정서윤</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -631,152 +631,152 @@
       <c r="B1" t="inlineStr"/>
       <c r="C1" t="inlineStr">
         <is>
+          <t>이완희</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>이예빈</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>정서윤</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>오서진</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>이완희</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>한예린</t>
+          <t>오서진</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>최세희</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>김소아</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>고동연</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>이동진</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>정미지</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>정예원</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>강건우</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>박세은</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>김소아</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>반주은</t>
+          <t>김지호</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>이지예</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>신우진</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>김나경</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>백지우</t>
+          <t>이나연</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>김지호</t>
+          <t>장윤서</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>장윤성</t>
+          <t>조하진</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>조하진</t>
+          <t>김나경</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>이나연</t>
+          <t>임다인</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>장윤서</t>
+          <t>김승연</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>최세희</t>
+          <t>김예담</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>이동진</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>김나연</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>장서윤</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>김예담</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>강건우</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>이지예</t>
+          <t>한예린</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이예빈</t>
+          <t>반주은</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>임다인</t>
+          <t>백지우</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>김승연</t>
+          <t>장윤성</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>김나연</t>
+          <t>정예원</t>
         </is>
       </c>
     </row>

--- a/자리표.xlsx
+++ b/자리표.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,156 +461,133 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>정예원</t>
+          <t>김미정</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>장윤성</t>
+          <t>신지아</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>백지우</t>
+          <t>최정남</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>반주은</t>
+          <t>오지아</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>한예린</t>
+          <t>김정호</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>장서윤</t>
+          <t>권영숙</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>김나연</t>
+          <t>이민재</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>이동진</t>
+          <t>장민지</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>김예담</t>
+          <t>최시우</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>김승연</t>
+          <t>김도윤</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>임다인</t>
+          <t>김경수</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>김나경</t>
+          <t>노상현</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>조하진</t>
+          <t>김하은</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>장윤서</t>
+          <t>오명자</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>이나연</t>
+          <t>김준호</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>신우진</t>
+          <t>최준혁</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>이지예</t>
+          <t>김미정</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>김지호</t>
+          <t>김민재</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>박세은</t>
+          <t>박경수</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>강건우</t>
+          <t>최상현</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>정미지</t>
+          <t>박지민</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>고동연</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>김소아</t>
-        </is>
-      </c>
+          <t>박현주</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>최세희</t>
+          <t>이옥순</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오서진</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>정서윤</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>이예빈</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>이완희</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>백채원</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -623,203 +600,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>이완희</t>
-        </is>
-      </c>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>백채원</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>이옥순</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr">
         <is>
-          <t>이예빈</t>
+          <t>박현주</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>정서윤</t>
+          <t>박지민</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>오서진</t>
+          <t>최상현</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>최세희</t>
+          <t>박경수</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>김소아</t>
+          <t>김민재</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>고동연</t>
+          <t>김미정</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>정미지</t>
+          <t>최준혁</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>강건우</t>
+          <t>김준호</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>박세은</t>
+          <t>오명자</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>김지호</t>
+          <t>김하은</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이지예</t>
+          <t>노상현</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>신우진</t>
+          <t>김경수</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>이나연</t>
+          <t>김도윤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>장윤서</t>
+          <t>최시우</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>조하진</t>
+          <t>장민지</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>김나경</t>
+          <t>이민재</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>임다인</t>
+          <t>권영숙</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>김승연</t>
+          <t>김정호</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>김예담</t>
+          <t>오지아</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>이동진</t>
+          <t>최정남</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>김나연</t>
+          <t>신지아</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>장서윤</t>
+          <t>김미정</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>한예린</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>반주은</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>백지우</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>장윤성</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>정예원</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/자리표.xlsx
+++ b/자리표.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,34 +461,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>이민재</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>이옥순</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>김미정</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>신지아</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>최정남</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>오지아</t>
+          <t>김미정</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>김정호</t>
+          <t>장민지</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>권영숙</t>
+          <t>노상현</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -498,94 +498,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>노상현</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>이옥순</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>장민지</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>최시우</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>김도윤</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>김경수</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>노상현</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>김하은</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>오명자</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>김준호</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>최준혁</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>김미정</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>김민재</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>박경수</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>최상현</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>박지민</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>박현주</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>이옥순</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>백채원</t>
         </is>
       </c>
     </row>
@@ -600,13 +523,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>백채원</t>
+          <t>장민지</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -614,166 +537,89 @@
           <t>이옥순</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>노상현</t>
+        </is>
+      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>박현주</t>
+          <t>이민재</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>박지민</t>
+          <t>노상현</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>최상현</t>
+          <t>장민지</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>박경수</t>
+          <t>김미정</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>김민재</t>
+          <t>김미정</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>김미정</t>
+          <t>이옥순</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>최준혁</t>
+          <t>이민재</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>김준호</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>오명자</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>김하은</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>노상현</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>김경수</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>김도윤</t>
+          <t>칠판</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>최시우</t>
+          <t>칠판</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>장민지</t>
+          <t>칠판</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이민재</t>
+          <t>칠판</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>권영숙</t>
+          <t>칠판</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>김정호</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>오지아</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>최정남</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>신지아</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>김미정</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/자리표.xlsx
+++ b/자리표.xlsx
@@ -497,71 +497,71 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -571,41 +571,41 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -665,41 +665,41 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -709,71 +709,71 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/자리표.xlsx
+++ b/자리표.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,7 +28,10 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <sz val="40"/>
+    </font>
+    <font>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -70,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -78,6 +81,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,14 +447,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,131 +501,138 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>김준영</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>김서연</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>이영자</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>이성진</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>이병철</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>정정수</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>박정순</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>윤지원</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>김은주</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>허수민</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>김하윤</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>김정희</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>김현우</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>김현준</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>손준혁</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>김성현</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>김성훈</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>김성현</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>김현준</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>박정자</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="inlineStr"/>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr"/>
+          <t>임영숙</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>이우진</t>
+        </is>
+      </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>김현지</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>안정웅</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>제작 날짜 : 2025.04.12</t>
         </is>
       </c>
     </row>
@@ -636,144 +647,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>안정웅</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr"/>
+          <t>김현지</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>이우진</t>
+        </is>
+      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>임영숙</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>박정자</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>김현준</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>김성현</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>김성훈</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>김성현</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>손준혁</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>김현준</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>김현우</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>김정희</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>김하윤</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>허수민</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>김은주</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>윤지원</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>박정순</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>정정수</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>이병철</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>이성진</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>이영자</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>김서연</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>김준영</t>
         </is>
       </c>
     </row>
@@ -818,6 +829,13 @@
       <c r="D8" s="1" t="inlineStr"/>
       <c r="E8" s="1" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>제작 날짜 : 2025.04.12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/자리표.xlsx
+++ b/자리표.xlsx
@@ -501,131 +501,131 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>김준영</t>
+          <t>장정희</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>김서연</t>
+          <t>이현우</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>이영자</t>
+          <t>황미영</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>이성진</t>
+          <t>김성호</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>이병철</t>
+          <t>박민준</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>정정수</t>
+          <t>노현우</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>박정순</t>
+          <t>김영희</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>윤지원</t>
+          <t>김영진</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>김은주</t>
+          <t>이수민</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>허수민</t>
+          <t>이지아</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>김하윤</t>
+          <t>문순자</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>김정희</t>
+          <t>조건우</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>김현우</t>
+          <t>황준호</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>김현준</t>
+          <t>박광수</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>손준혁</t>
+          <t>심경희</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>김성현</t>
+          <t>김성훈</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>김성훈</t>
+          <t>이영길</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>김성현</t>
+          <t>이순자</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>김현준</t>
+          <t>김재현</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>박정자</t>
+          <t>이서영</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>임영숙</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>이옥자</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>이우진</t>
+          <t>김지훈</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>김현지</t>
+          <t>이중수</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>안정웅</t>
+          <t>김미정</t>
         </is>
       </c>
     </row>
@@ -660,131 +660,131 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>안정웅</t>
+          <t>김미정</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>김현지</t>
+          <t>이중수</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>이우진</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>임영숙</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr"/>
+          <t>김지훈</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>이옥자</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>박정자</t>
+          <t>이서영</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>김현준</t>
+          <t>김재현</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>김성현</t>
+          <t>이순자</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>이영길</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
           <t>김성훈</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>김성현</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>손준혁</t>
+          <t>심경희</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>김현준</t>
+          <t>박광수</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>김현우</t>
+          <t>황준호</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>김정희</t>
+          <t>조건우</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>김하윤</t>
+          <t>문순자</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>허수민</t>
+          <t>이지아</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>김은주</t>
+          <t>이수민</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>윤지원</t>
+          <t>김영진</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>박정순</t>
+          <t>김영희</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>정정수</t>
+          <t>노현우</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>이병철</t>
+          <t>박민준</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>이성진</t>
+          <t>김성호</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>이영자</t>
+          <t>황미영</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>김서연</t>
+          <t>이현우</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>김준영</t>
+          <t>장정희</t>
         </is>
       </c>
     </row>

--- a/자리표.xlsx
+++ b/자리표.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -501,136 +501,159 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>장정희</t>
+          <t>김승연</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>이현우</t>
+          <t>김소아</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>황미영</t>
+          <t>신우진</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>김성호</t>
+          <t>이지예</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>박민준</t>
+          <t>김지호</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>노현우</t>
+          <t>정미지</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>장서윤</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>김영진</t>
+          <t>고동연</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>이수민</t>
+          <t>이예빈</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>이지아</t>
+          <t>김예담</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>문순자</t>
+          <t>이동진</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>조건우</t>
+          <t>이나연</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>황준호</t>
+          <t>임다인</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>박광수</t>
+          <t>장윤성</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>심경희</t>
+          <t>백지우</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>김성훈</t>
+          <t>반주은</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>이영길</t>
+          <t>오서진</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>이순자</t>
+          <t>이완희</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>김재현</t>
+          <t>장윤서</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>이서영</t>
+          <t>박세은</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>이옥자</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr"/>
+          <t>최세희</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>한예린</t>
+        </is>
+      </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>김지훈</t>
+          <t>조하진</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>이중수</t>
+          <t>정예원</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>김미정</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+          <t>정서윤</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>김나연</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>김나경</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>강건우</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>제작 날짜 : 2025.04.12</t>
         </is>
@@ -647,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -658,179 +681,202 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>김미정</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>이중수</t>
-        </is>
-      </c>
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr"/>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>김지훈</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr"/>
+          <t>강건우</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>김나경</t>
+        </is>
+      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>이옥자</t>
+          <t>김나연</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>이서영</t>
+          <t>정서윤</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>김재현</t>
+          <t>정예원</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>이순자</t>
+          <t>조하진</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>이영길</t>
+          <t>한예린</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>김성훈</t>
+          <t>최세희</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>심경희</t>
+          <t>박세은</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>박광수</t>
+          <t>장윤서</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>황준호</t>
+          <t>이완희</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>조건우</t>
+          <t>오서진</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>문순자</t>
+          <t>반주은</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>이지아</t>
+          <t>백지우</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>이수민</t>
+          <t>장윤성</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>김영진</t>
+          <t>임다인</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>이나연</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>노현우</t>
+          <t>이동진</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>박민준</t>
+          <t>김예담</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>김성호</t>
+          <t>이예빈</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>황미영</t>
+          <t>고동연</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>이현우</t>
+          <t>장서윤</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>장정희</t>
+          <t>정미지</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr"/>
-      <c r="D6" s="1" t="inlineStr"/>
-      <c r="E6" s="1" t="inlineStr"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>김지호</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>이지예</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>신우진</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>김소아</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>김승연</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr"/>
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr"/>
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>제작 날짜 : 2025.04.12</t>
         </is>

--- a/자리표.xlsx
+++ b/자리표.xlsx
@@ -10,7 +10,9 @@
     <sheet name="학생 관점" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="교사 관점" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'교사 관점'!$A$1:$E$15</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,9 +30,13 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="40"/>
+      <sz val="22"/>
     </font>
     <font>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -73,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -82,6 +88,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,14 +454,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,161 +508,122 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>김승연</t>
+          <t>류정수</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>김소아</t>
+          <t>서민재</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>신우진</t>
+          <t>윤승민</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>이지예</t>
+          <t>박선영</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>김지호</t>
+          <t>류진호</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>정미지</t>
+          <t>김지현</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>장서윤</t>
+          <t>오준서</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>고동연</t>
+          <t>백현준</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>이예빈</t>
+          <t>임은정</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>김예담</t>
+          <t>김광수</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>이동진</t>
+          <t>김민재</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>이나연</t>
+          <t>김상훈</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>임다인</t>
+          <t>김진호</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>장윤성</t>
+          <t>이하윤</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>백지우</t>
+          <t>황성진</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>반주은</t>
+          <t>이승민</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>오서진</t>
+          <t>백예지</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>이완희</t>
+          <t>김은서</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>장윤서</t>
+          <t>지준서</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>박세은</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>최세희</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>한예린</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>조하진</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>정예원</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>정서윤</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>김나연</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>김나경</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>강건우</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr"/>
-      <c r="E9" s="1" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+          <t>박영일</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>제작 날짜 : 2025.04.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">※ 이 시트는 학생이 보는 자리배치표입니다. 교사 관점 배치도는 아래의 다른 탭에서 확인해주세요. </t>
         </is>
       </c>
     </row>
@@ -670,167 +638,155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>박영일</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>지준서</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>강건우</t>
+          <t>김은서</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>김나경</t>
+          <t>백예지</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>김나연</t>
+          <t>이승민</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>정서윤</t>
+          <t>황성진</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>정예원</t>
+          <t>이하윤</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>조하진</t>
+          <t>김진호</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>한예린</t>
+          <t>김상훈</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>최세희</t>
+          <t>김민재</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>박세은</t>
+          <t>김광수</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>장윤서</t>
+          <t>임은정</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>이완희</t>
+          <t>백현준</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>오서진</t>
+          <t>오준서</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>반주은</t>
+          <t>김지현</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>백지우</t>
+          <t>류진호</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>장윤성</t>
+          <t>박선영</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>임다인</t>
+          <t>윤승민</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>이나연</t>
+          <t>서민재</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>이동진</t>
+          <t>류정수</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>김예담</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>이예빈</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>고동연</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>장서윤</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>정미지</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr"/>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr"/>
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>김지호</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>이지예</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>신우진</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>김소아</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>김승연</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
         </is>
       </c>
     </row>
@@ -841,48 +797,22 @@
       <c r="D7" s="1" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr"/>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr"/>
-      <c r="D9" s="1" t="inlineStr"/>
-      <c r="E9" s="1" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>제작 날짜 : 2025.04.12</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">※ 이 시트는 교사가 보는 자리배치표입니다. 학생 관점 배치도는 아래의 다른 탭에서 확인해주세요. </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/자리표.xlsx
+++ b/자리표.xlsx
@@ -30,7 +30,7 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="22"/>
+      <sz val="40"/>
     </font>
     <font>
       <sz val="12"/>
@@ -457,11 +457,11 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,29 +513,29 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>서민재</t>
+          <t>김광수</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>윤승민</t>
+          <t>이하윤</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>박선영</t>
+          <t>김진호</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>류진호</t>
+          <t>임은정</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>김지현</t>
+          <t>박선영</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
@@ -550,66 +550,66 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>임은정</t>
+          <t>박영일</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>김광수</t>
+          <t>김은서</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>지준서</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>황성진</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
           <t>김민재</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>김상훈</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>김진호</t>
-        </is>
-      </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>이하윤</t>
+          <t>류진호</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>황성진</t>
+          <t>김지현</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>윤승민</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>서민재</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>김상훈</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>백예지</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
           <t>이승민</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>백예지</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>김은서</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>지준서</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>박영일</t>
         </is>
       </c>
     </row>
@@ -641,76 +641,76 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>박영일</t>
+          <t>이승민</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>지준서</t>
+          <t>백예지</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>김은서</t>
+          <t>김상훈</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>백예지</t>
+          <t>서민재</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>이승민</t>
+          <t>윤승민</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
+          <t>김지현</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>류진호</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>김민재</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>황성진</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>이하윤</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>김진호</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>김상훈</t>
-        </is>
-      </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>김민재</t>
+          <t>지준서</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>김광수</t>
+          <t>김은서</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>임은정</t>
+          <t>박영일</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -725,29 +725,29 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>김지현</t>
+          <t>박선영</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>류진호</t>
+          <t>임은정</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>박선영</t>
+          <t>김진호</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>윤승민</t>
+          <t>이하윤</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>서민재</t>
+          <t>김광수</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">

--- a/자리표.xlsx
+++ b/자리표.xlsx
@@ -11,7 +11,7 @@
     <sheet name="교사 관점" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'교사 관점'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'교사 관점'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -508,120 +508,139 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>류정수</t>
+          <t>김옥자</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>김광수</t>
+          <t>김도윤</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>이하윤</t>
+          <t>박병철</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>김진호</t>
+          <t>최하은</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>임은정</t>
+          <t>이준서</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>박선영</t>
+          <t>이영환</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>오준서</t>
+          <t>이준서</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>백현준</t>
+          <t>곽명숙</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>박영일</t>
+          <t>홍현준</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>김은서</t>
+          <t>최준영</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>지준서</t>
+          <t>안지아</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>황성진</t>
+          <t>손하윤</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>김민재</t>
+          <t>이주원</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>류진호</t>
+          <t>김경희</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>김지현</t>
+          <t>김지후</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>윤승민</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>서민재</t>
-        </is>
-      </c>
+          <t>김영호</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>김상훈</t>
+          <t>신정식</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>백예지</t>
+          <t>김도현</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>이승민</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+          <t>이우진</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>김유진</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>송승현</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>박중수</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>장정순</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>제작 날짜 : 2025.04.12</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">※ 이 시트는 학생이 보는 자리배치표입니다. 교사 관점 배치도는 아래의 다른 탭에서 확인해주세요. </t>
         </is>
@@ -638,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -651,161 +670,180 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>이승민</t>
+          <t>장정순</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>백예지</t>
+          <t>박중수</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>김상훈</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>서민재</t>
-        </is>
-      </c>
+          <t>송승현</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr"/>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>윤승민</t>
+          <t>김유진</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>김지현</t>
+          <t>이우진</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>류진호</t>
+          <t>김도현</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>김민재</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>황성진</t>
-        </is>
-      </c>
+          <t>신정식</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>지준서</t>
+          <t>김영호</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>김은서</t>
+          <t>김지후</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>박영일</t>
+          <t>김경희</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>백현준</t>
+          <t>이주원</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>오준서</t>
+          <t>손하윤</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>박선영</t>
+          <t>안지아</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>임은정</t>
+          <t>최준영</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>김진호</t>
+          <t>홍현준</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>이하윤</t>
+          <t>곽명숙</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>김광수</t>
+          <t>이준서</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>류정수</t>
+          <t>이영환</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr"/>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr"/>
-      <c r="D5" s="1" t="inlineStr"/>
-      <c r="E5" s="1" t="inlineStr"/>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>이준서</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>최하은</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>박병철</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>김도윤</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>김옥자</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>칠판</t>
-        </is>
-      </c>
+      <c r="A6" s="1" t="inlineStr"/>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr"/>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>칠판</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr"/>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>제작 날짜 : 2025.04.12</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">※ 이 시트는 교사가 보는 자리배치표입니다. 학생 관점 배치도는 아래의 다른 탭에서 확인해주세요. </t>
         </is>
